--- a/shared/reporte_acumulado_procesado/2026-06_procesado.xlsx
+++ b/shared/reporte_acumulado_procesado/2026-06_procesado.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,7 +68,7 @@
     </font>
     <font>
       <name val="Courier New"/>
-      <color rgb="00085041"/>
+      <color rgb="007C3003"/>
       <sz val="10"/>
     </font>
     <font>
@@ -93,7 +93,17 @@
     </font>
     <font>
       <name val="Courier New"/>
-      <color rgb="007C3003"/>
+      <color rgb="007D6608"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00085041"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="000C447C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -103,22 +113,7 @@
     </font>
     <font>
       <name val="Courier New"/>
-      <color rgb="000C447C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
       <color rgb="001D4ED8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="00A32D2D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="007D6608"/>
       <sz val="10"/>
     </font>
     <font>
@@ -127,7 +122,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -192,11 +187,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EFF6FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCEBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +309,7 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -340,25 +330,25 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -726,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -889,17 +879,17 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>U0451</t>
+          <t>U0371</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>JENNY LINO ILLAJANQUI</t>
+          <t>VICKI MASIAS CUSIHUAMAN</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D3" s="4" t="n"/>
@@ -915,62 +905,62 @@
       </c>
       <c r="G3" s="17" t="n"/>
       <c r="H3" s="18" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="I3" s="18" t="n"/>
       <c r="J3" s="19" t="inlineStr">
         <is>
-          <t>c1-7</t>
+          <t>Vicky Masías. W4?</t>
         </is>
       </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
-          <t>11/06/2026 18:37:29</t>
+          <t>15/06/2026 21:13:40</t>
         </is>
       </c>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="20" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>W</t>
         </is>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O3" s="21" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="22" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R3" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S3" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T3" s="4" t="n"/>
-      <c r="U3" s="23" t="n">
+      <c r="U3" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>U0087</t>
+          <t>U0033</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>YOLANDA MATILDE MONTALVO COSME</t>
+          <t>ODILON CERNA ROMERO</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
@@ -981,28 +971,28 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Janet Vil*</t>
+          <t>Sonia Cer*</t>
         </is>
       </c>
       <c r="G4" s="17" t="n"/>
       <c r="H4" s="18" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="I4" s="18" t="n"/>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>E1 1 tanque</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>10/06/2026 19:08:13</t>
+          <t>15/06/2026 14:25:29</t>
         </is>
       </c>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N4" s="20" t="inlineStr">
@@ -1013,35 +1003,35 @@
       <c r="O4" s="21" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R4" s="22" t="n">
-        <v>92</v>
-      </c>
-      <c r="S4" s="24" t="inlineStr">
-        <is>
-          <t>exceso</t>
+        <v>0</v>
+      </c>
+      <c r="S4" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T4" s="4" t="n"/>
-      <c r="U4" s="23" t="n">
+      <c r="U4" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>U0332</t>
+          <t>U0451</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>JACINTA AMEZ AGUIRRE</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>JENNY LINO ILLAJANQUI</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -1052,59 +1042,67 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Herlinda Ang*</t>
+          <t>Wilder Tru*</t>
         </is>
       </c>
       <c r="G5" s="17" t="n"/>
       <c r="H5" s="18" t="n">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="I5" s="18" t="n"/>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>Jacinta amez aguirre</t>
+          <t>c1-7</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>10/06/2026 18:14:42</t>
+          <t>11/06/2026 18:37:29</t>
         </is>
       </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="20" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O5" s="21" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S5" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T5" s="4" t="n"/>
-      <c r="U5" s="23" t="n">
+      <c r="U5" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="14" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>U0087</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>YOLANDA MATILDE MONTALVO COSME</t>
+        </is>
+      </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>blanco</t>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
@@ -1115,63 +1113,67 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>Sthefany Cre*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G6" s="17" t="n"/>
       <c r="H6" s="18" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="I6" s="18" t="n"/>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>E1 1 tanque</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>10/06/2026 12:52:36</t>
+          <t>10/06/2026 19:08:13</t>
         </is>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="20" t="inlineStr">
         <is>
-          <t>BLANCO</t>
-        </is>
-      </c>
-      <c r="N6" s="20" t="n"/>
-      <c r="O6" s="21" t="inlineStr">
-        <is>
-          <t>BLANCO</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="22" t="n"/>
-      <c r="R6" s="22" t="n"/>
-      <c r="S6" s="26" t="inlineStr">
-        <is>
-          <t>concepto</t>
+      <c r="Q6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T6" s="4" t="n"/>
-      <c r="U6" s="23" t="n">
+      <c r="U6" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>U0068</t>
+          <t>U0332</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>JANET ROMERO MAYO</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>JACINTA AMEZ AGUIRRE</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D7" s="4" t="n"/>
@@ -1182,67 +1184,59 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>Janet Rom*</t>
+          <t>Herlinda Ang*</t>
         </is>
       </c>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="18" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="I7" s="18" t="n"/>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>Mz:c Lt:39(Janet Romero Mayo)</t>
+          <t>Jacinta amez aguirre</t>
         </is>
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 20:24:02</t>
+          <t>10/06/2026 18:14:42</t>
         </is>
       </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O7" s="21" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="22" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S7" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T7" s="4" t="n"/>
-      <c r="U7" s="23" t="n">
+      <c r="U7" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>U0213</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>RAUL OLIVO CORDOVA</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>blanco</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
@@ -1253,65 +1247,61 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>Claudia Can*</t>
+          <t>Sthefany Cre*</t>
         </is>
       </c>
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="18" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I8" s="18" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>Mz L lote 5 Micaela Bastidas. Raúl Córdoba.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 20:19:01</t>
+          <t>10/06/2026 12:52:36</t>
         </is>
       </c>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="20" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n"/>
+          <t>BLANCO</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>BLANCO</t>
+        </is>
+      </c>
       <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="22" t="n">
-        <v>116</v>
-      </c>
-      <c r="R8" s="22" t="n">
-        <v>-100</v>
-      </c>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
       <c r="S8" s="27" t="inlineStr">
         <is>
-          <t>parcial</t>
+          <t>concepto</t>
         </is>
       </c>
       <c r="T8" s="4" t="n"/>
-      <c r="U8" s="23" t="n">
+      <c r="U8" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>U0081</t>
+          <t>U0068</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>MARTINA MENDOZA ROMERO</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
+          <t>JANET ROMERO MAYO</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -1324,65 +1314,65 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>Liliana Req*</t>
+          <t>Janet Rom*</t>
         </is>
       </c>
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="18" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="I9" s="18" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>Mz d lt 12</t>
+          <t>Mz:c Lt:39(Janet Romero Mayo)</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 19:34:26</t>
+          <t>09/06/2026 20:24:02</t>
         </is>
       </c>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O9" s="21" t="n"/>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="22" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S9" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T9" s="4" t="n"/>
-      <c r="U9" s="23" t="n">
+      <c r="U9" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>U0101</t>
+          <t>U0213</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>MERCADO TUPAC AMARU</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+          <t>RAUL OLIVO CORDOVA</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -1395,65 +1385,65 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>Rimenita Mun*</t>
+          <t>Claudia Can*</t>
         </is>
       </c>
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I10" s="18" t="n"/>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>MZ.  E.      LT 19</t>
+          <t>Mz L lote 5 Micaela Bastidas. Raúl Córdoba.</t>
         </is>
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 19:13:14</t>
+          <t>09/06/2026 20:19:01</t>
         </is>
       </c>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="21" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S10" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T10" s="4" t="n"/>
-      <c r="U10" s="23" t="n">
+      <c r="U10" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>U0118</t>
+          <t>U0081</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>RAQUEL MABEL AVILA MORALES</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+          <t>MARTINA MENDOZA ROMERO</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -1466,65 +1456,65 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>Janet Vil*</t>
+          <t>Liliana Req*</t>
         </is>
       </c>
       <c r="G11" s="17" t="n"/>
       <c r="H11" s="18" t="n">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="I11" s="18" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>mz G lt 3</t>
+          <t>Mz d lt 12</t>
         </is>
       </c>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 11:55:11</t>
+          <t>09/06/2026 19:34:26</t>
         </is>
       </c>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="20" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O11" s="21" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="22" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S11" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T11" s="4" t="n"/>
-      <c r="U11" s="23" t="n">
+      <c r="U11" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>U0148</t>
+          <t>U0101</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>CLEMENTE RODRIGUEZ ROJAS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+          <t>MERCADO TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -1537,67 +1527,67 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>Alberto Rod*</t>
+          <t>Rimenita Mun*</t>
         </is>
       </c>
       <c r="G12" s="17" t="n"/>
       <c r="H12" s="18" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="I12" s="18" t="n"/>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>Mz H lote 9 Clemente Rodriguez Rojas</t>
+          <t>MZ.  E.      LT 19</t>
         </is>
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 11:50:58</t>
+          <t>09/06/2026 19:13:14</t>
         </is>
       </c>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="20" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="22" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S12" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T12" s="4" t="n"/>
-      <c r="U12" s="23" t="n">
+      <c r="U12" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>U0082</t>
+          <t>U0118</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>ROSELA ELVIRA MUÑOZ HERMITAÑO</t>
-        </is>
-      </c>
-      <c r="C13" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>RAQUEL MABEL AVILA MORALES</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D13" s="4" t="n"/>
@@ -1608,65 +1598,65 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>Rosela Mun*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G13" s="17" t="n"/>
       <c r="H13" s="18" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="I13" s="18" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mz G lt 3</t>
         </is>
       </c>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>09/06/2026 08:31:47</t>
+          <t>09/06/2026 11:55:11</t>
         </is>
       </c>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" s="21" t="n"/>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S13" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T13" s="4" t="n"/>
-      <c r="U13" s="23" t="n">
+      <c r="U13" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>U0195</t>
+          <t>U0148</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>ANTONIO ESPINOZA SIFUENTES</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+          <t>CLEMENTE RODRIGUEZ ROJAS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -1679,67 +1669,67 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Paul Tru*</t>
+          <t>Alberto Rod*</t>
         </is>
       </c>
       <c r="G14" s="17" t="n"/>
       <c r="H14" s="18" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="I14" s="18" t="n"/>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>Mz k lt 2</t>
+          <t>Mz H lote 9 Clemente Rodriguez Rojas</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 18:09:36</t>
+          <t>09/06/2026 11:50:58</t>
         </is>
       </c>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="20" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O14" s="21" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="22" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S14" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T14" s="4" t="n"/>
-      <c r="U14" s="23" t="n">
+      <c r="U14" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>U0155</t>
+          <t>U0082</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>GREGORIO TOLENTINO SANCHEZ</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>ROSELA ELVIRA MUÑOZ HERMITAÑO</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
@@ -1750,12 +1740,12 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>Delia Cam*</t>
+          <t>Rosela Mun*</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="18" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I15" s="18" t="n"/>
       <c r="J15" s="19" t="inlineStr">
@@ -1765,50 +1755,50 @@
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 17:32:20</t>
+          <t>09/06/2026 08:31:47</t>
         </is>
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="20" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O15" s="21" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R15" s="22" t="n">
-        <v>-75</v>
-      </c>
-      <c r="S15" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S15" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T15" s="4" t="n"/>
-      <c r="U15" s="23" t="n">
+      <c r="U15" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>U0175</t>
+          <t>U0195</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>JULIO SOLORZANO ESTRADA</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
+          <t>ANTONIO ESPINOZA SIFUENTES</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -1821,57 +1811,65 @@
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>Walter Sol*</t>
+          <t>Paul Tru*</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
       <c r="H16" s="18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I16" s="18" t="n"/>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>i 13 Julio Solorzano</t>
+          <t>Mz k lt 2</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 11:04:34</t>
+          <t>07/06/2026 18:09:36</t>
         </is>
       </c>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O16" s="21" t="n"/>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S16" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T16" s="4" t="n"/>
-      <c r="U16" s="23" t="n">
+      <c r="U16" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>U0155</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>GREGORIO TOLENTINO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>correccion</t>
         </is>
@@ -1884,51 +1882,67 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>Janet Vil*</t>
+          <t>Delia Cam*</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
       <c r="H17" s="18" t="n">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="I17" s="18" t="n"/>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t>geral cobro de agua</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 10:39:56</t>
+          <t>07/06/2026 17:32:20</t>
         </is>
       </c>
       <c r="L17" s="4" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="21" t="inlineStr">
-        <is>
-          <t>cobro de agua (Yerald)</t>
-        </is>
-      </c>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="n"/>
       <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="22" t="n"/>
-      <c r="R17" s="22" t="n"/>
-      <c r="S17" s="26" t="inlineStr">
-        <is>
-          <t>concepto</t>
+      <c r="Q17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T17" s="4" t="n"/>
-      <c r="U17" s="23" t="n">
+      <c r="U17" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="14" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>U0175</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>JULIO SOLORZANO ESTRADA</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
@@ -1939,59 +1953,67 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>Janet Vil*</t>
+          <t>Walter Sol*</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>
       <c r="H18" s="18" t="n">
-        <v>450</v>
+        <v>51</v>
       </c>
       <c r="I18" s="18" t="n"/>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>350#1cobro 100 # cobro maximo</t>
+          <t>i 13 Julio Solorzano</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 10:39:01</t>
+          <t>07/06/2026 11:04:34</t>
         </is>
       </c>
       <c r="L18" s="4" t="n"/>
-      <c r="M18" s="20" t="n"/>
-      <c r="N18" s="20" t="n"/>
-      <c r="O18" s="21" t="inlineStr">
-        <is>
-          <t>cobro de agua (Maximo)</t>
-        </is>
-      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="22" t="n"/>
-      <c r="S18" s="26" t="inlineStr">
-        <is>
-          <t>concepto</t>
+      <c r="Q18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T18" s="4" t="n"/>
-      <c r="U18" s="23" t="n">
+      <c r="U18" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>U0469</t>
+          <t>U0199</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>JULIO VEGA CERDA</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>NIEVES CUZCO VALLE DE LEON</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -2002,67 +2024,67 @@
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>Julio Veg*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="18" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I19" s="18" t="n"/>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mz E1 Lte 8. de faenas están canceladas. por lo que no </t>
+          <t>geral cobro de agua</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 10:08:59</t>
+          <t>07/06/2026 10:39:56</t>
         </is>
       </c>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="20" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>K</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="21" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="22" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R19" s="22" t="n">
-        <v>-31</v>
-      </c>
-      <c r="S19" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S19" s="24" t="inlineStr">
+        <is>
+          <t>exacto</t>
         </is>
       </c>
       <c r="T19" s="4" t="n"/>
-      <c r="U19" s="23" t="n">
+      <c r="U19" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>U0464</t>
+          <t>U0472</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>JHONNY SALOMON NIÑO ORTIZ</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>ANI CRUZ DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D20" s="4" t="n"/>
@@ -2073,67 +2095,59 @@
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>Renee Med*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="18" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I20" s="18" t="n"/>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johnny Salomón Niño Ortiz (Mz E1 lote 1) (exonerado </t>
+          <t>geral cobro de agua</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 09:08:06</t>
+          <t>07/06/2026 10:39:56</t>
         </is>
       </c>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="20" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O20" s="21" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="22" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R20" s="22" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S20" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S20" s="24" t="inlineStr">
+        <is>
+          <t>exacto</t>
         </is>
       </c>
       <c r="T20" s="4" t="n"/>
-      <c r="U20" s="23" t="n">
+      <c r="U20" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>U0426</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>ALBERTO CHINCHAY PARIAMACHI</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
@@ -2144,67 +2158,67 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>Sandra Del*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="18" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="I21" s="18" t="n"/>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">mza.A1 lote 4 Alberto chinchay pariamachi  </t>
+          <t>geral cobro de agua</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>07/06/2026 08:27:29</t>
+          <t>07/06/2026 10:39:56</t>
         </is>
       </c>
       <c r="L21" s="4" t="n"/>
       <c r="M21" s="20" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="O21" s="21" t="n"/>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R21" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="16" t="inlineStr">
+      <c r="S21" s="24" t="inlineStr">
         <is>
           <t>exacto</t>
         </is>
       </c>
       <c r="T21" s="4" t="n"/>
-      <c r="U21" s="23" t="n">
+      <c r="U21" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>U0264</t>
+          <t>U0480</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>EDGAR MELGAREJO BEDON</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>ESTELA FLORES LOAYZA</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -2215,7 +2229,7 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Edgar Mel*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -2225,57 +2239,57 @@
       <c r="I22" s="18" t="n"/>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>mz o lt 16 Edgar melgarejo</t>
+          <t>geral cobro de agua</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 22:48:23</t>
+          <t>07/06/2026 10:39:56</t>
         </is>
       </c>
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O22" s="21" t="n"/>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R22" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S22" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S22" s="24" t="inlineStr">
+        <is>
+          <t>exacto</t>
         </is>
       </c>
       <c r="T22" s="4" t="n"/>
-      <c r="U22" s="23" t="n">
+      <c r="U22" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>U0010</t>
+          <t>U0271</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>ALEJANDRO MELGAREJO ESPINOZA</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>MARIA HUERTA MILLA</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D23" s="4" t="n"/>
@@ -2286,67 +2300,71 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>Jose Mel*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="18" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="I23" s="18" t="n"/>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pago del servicio de agua, usuario Alejandro Melgarejo, </t>
+          <t>350#1cobro 100 # cobro maximo</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 21:59:44</t>
+          <t>07/06/2026 10:39:01</t>
         </is>
       </c>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>O</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O23" s="21" t="n"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="22" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="R23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="16" t="inlineStr">
+      <c r="S23" s="24" t="inlineStr">
         <is>
           <t>exacto</t>
         </is>
       </c>
       <c r="T23" s="4" t="n"/>
-      <c r="U23" s="23" t="n">
+      <c r="U23" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>U0288</t>
+          <t>U0272</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>JUDITH VENTURO ROSALES</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>REYNA HUERTA MILLA</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D24" s="4" t="n"/>
@@ -2357,67 +2375,63 @@
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>Judith Ven*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="18" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="I24" s="18" t="n"/>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>manzana P lote 12</t>
+          <t>350#1cobro 100 # cobro maximo</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 21:46:01</t>
+          <t>07/06/2026 10:39:01</t>
         </is>
       </c>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O24" s="21" t="n"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="22" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="16" t="inlineStr">
+      <c r="S24" s="24" t="inlineStr">
         <is>
           <t>exacto</t>
         </is>
       </c>
       <c r="T24" s="4" t="n"/>
-      <c r="U24" s="23" t="n">
+      <c r="U24" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>U0105</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>TOLENTINO JULCA MORENO</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>comunitario</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -2428,65 +2442,69 @@
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>Elma Rom*</t>
+          <t>Janet Vil*</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="18" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="I25" s="18" t="n"/>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t>mz f lote 4 tolentino julca</t>
+          <t>350#1cobro 100 # cobro maximo</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 21:44:17</t>
+          <t>07/06/2026 10:39:01</t>
         </is>
       </c>
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O25" s="21" t="n"/>
+          <t>BLANCO</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>tanque</t>
+        </is>
+      </c>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="22" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R25" s="22" t="n">
-        <v>-125</v>
-      </c>
-      <c r="S25" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S25" s="24" t="inlineStr">
+        <is>
+          <t>exacto</t>
         </is>
       </c>
       <c r="T25" s="4" t="n"/>
-      <c r="U25" s="23" t="n">
+      <c r="U25" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>U0039</t>
+          <t>U0469</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>JULISSA BARRETO QUITO</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
+          <t>JULIO VEGA CERDA</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -2499,28 +2517,28 @@
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>Julissa Bar*</t>
+          <t>Julio Veg*</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
       <c r="H26" s="18" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="I26" s="18" t="n"/>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>Mz C LT 8</t>
+          <t xml:space="preserve">Mz E1 Lte 8. de faenas están canceladas. por lo que no </t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 21:26:17</t>
+          <t>07/06/2026 10:08:59</t>
         </is>
       </c>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -2531,33 +2549,33 @@
       <c r="O26" s="21" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="R26" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S26" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T26" s="4" t="n"/>
-      <c r="U26" s="23" t="n">
+      <c r="U26" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>U0166</t>
+          <t>U0464</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>EUGENIO LEONCIO MOYA DURAND</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
+          <t>JHONNY SALOMON NIÑO ORTIZ</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -2570,7 +2588,7 @@
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>Llitech Moy*</t>
+          <t>Renee Med*</t>
         </is>
       </c>
       <c r="G27" s="17" t="n"/>
@@ -2580,51 +2598,55 @@
       <c r="I27" s="18" t="n"/>
       <c r="J27" s="19" t="inlineStr">
         <is>
-          <t>Mz: i - Lt: 4</t>
+          <t xml:space="preserve">Johnny Salomón Niño Ortiz (Mz E1 lote 1) (exonerado </t>
         </is>
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 20:46:49</t>
+          <t>07/06/2026 09:08:06</t>
         </is>
       </c>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O27" s="21" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R27" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="S27" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S27" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T27" s="4" t="n"/>
-      <c r="U27" s="23" t="n">
+      <c r="U27" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="14" t="n"/>
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>U0426</t>
+        </is>
+      </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>SAORY RAPRAY SILVA</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
+          <t>ALBERTO CHINCHAY PARIAMACHI</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -2637,67 +2659,67 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>Melissa Pil*</t>
+          <t>Sandra Del*</t>
         </is>
       </c>
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="18" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="I28" s="18" t="n"/>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>Melissa MZB Lt 15</t>
+          <t xml:space="preserve">mza.A1 lote 4 Alberto chinchay pariamachi  </t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 19:19:54</t>
+          <t>07/06/2026 08:27:29</t>
         </is>
       </c>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="22" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R28" s="22" t="n">
-        <v>-55</v>
-      </c>
-      <c r="S28" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S28" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T28" s="4" t="n"/>
-      <c r="U28" s="23" t="n">
+      <c r="U28" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>U0446</t>
+          <t>U0264</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>AUBERTINA TRUJILLO TOLENTINO</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>EDGAR MELGAREJO BEDON</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -2708,62 +2730,62 @@
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>PLIN - WILLIAM MANUEL CUADROS CERREPE</t>
+          <t>Edgar Mel*</t>
         </is>
       </c>
       <c r="G29" s="17" t="n"/>
       <c r="H29" s="18" t="n">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="I29" s="18" t="n"/>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t>Aubertina Trujillo T</t>
+          <t>mz o lt 16 Edgar melgarejo</t>
         </is>
       </c>
       <c r="K29" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 18:48:11</t>
+          <t>06/06/2026 22:48:23</t>
         </is>
       </c>
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="20" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O29" s="21" t="n"/>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="22" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R29" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S29" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T29" s="4" t="n"/>
-      <c r="U29" s="23" t="n">
+      <c r="U29" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>U0393</t>
+          <t>U0010</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>FELIPE JESUS ORTIZ APONTE</t>
+          <t>ALEJANDRO MELGAREJO ESPINOZA</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
@@ -2779,65 +2801,65 @@
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>Felipe Ort*</t>
+          <t>Jose Mel*</t>
         </is>
       </c>
       <c r="G30" s="17" t="n"/>
       <c r="H30" s="18" t="n">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="I30" s="18" t="n"/>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t xml:space="preserve">pago del servicio de agua, usuario Alejandro Melgarejo, </t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 17:49:18</t>
+          <t>06/06/2026 21:59:44</t>
         </is>
       </c>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O30" s="21" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R30" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S30" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T30" s="4" t="n"/>
-      <c r="U30" s="23" t="n">
+      <c r="U30" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>U0097</t>
+          <t>U0288</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>TEOFILA FERNANDEZ REYES</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
+          <t>JUDITH VENTURO ROSALES</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -2850,28 +2872,28 @@
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>Grabiela Val*</t>
+          <t>Judith Ven*</t>
         </is>
       </c>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="18" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="I31" s="18" t="n"/>
       <c r="J31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEOFILA FERNANDEZ REYES MZ E Lt12 la loza se va </t>
+          <t>manzana P lote 12</t>
         </is>
       </c>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 17:23:01</t>
+          <t>06/06/2026 21:46:01</t>
         </is>
       </c>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>P</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -2882,33 +2904,33 @@
       <c r="O31" s="21" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="22" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R31" s="22" t="n">
-        <v>-51</v>
-      </c>
-      <c r="S31" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S31" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T31" s="4" t="n"/>
-      <c r="U31" s="23" t="n">
+      <c r="U31" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>U0372</t>
+          <t>U0105</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>RENATO ALBORNOS SIGUEÑAS</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
+          <t>TOLENTINO JULCA MORENO</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -2921,67 +2943,67 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>Marisol Rom*</t>
+          <t>Elma Rom*</t>
         </is>
       </c>
       <c r="G32" s="17" t="n"/>
       <c r="H32" s="18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I32" s="18" t="n"/>
       <c r="J32" s="19" t="inlineStr">
         <is>
-          <t>Mzn.W.Lt.5</t>
+          <t>mz f lote 4 tolentino julca</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 16:53:38</t>
+          <t>06/06/2026 21:44:17</t>
         </is>
       </c>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="20" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>F</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O32" s="21" t="n"/>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R32" s="22" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S32" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S32" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T32" s="4" t="n"/>
-      <c r="U32" s="23" t="n">
+      <c r="U32" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>U0434</t>
+          <t>U0039</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>JOHAN ENSO RODRIGUEZ FLORES</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>JULISSA BARRETO QUITO</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
@@ -2992,65 +3014,65 @@
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>Johan Rod*</t>
+          <t>Julissa Bar*</t>
         </is>
       </c>
       <c r="G33" s="17" t="n"/>
       <c r="H33" s="18" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I33" s="18" t="n"/>
       <c r="J33" s="19" t="inlineStr">
         <is>
-          <t>MZ, B1.Lt..3=Johan Rodriguez Flores</t>
+          <t>Mz C LT 8</t>
         </is>
       </c>
       <c r="K33" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 16:35:56</t>
+          <t>06/06/2026 21:26:17</t>
         </is>
       </c>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="20" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="21" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="22" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R33" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S33" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T33" s="4" t="n"/>
-      <c r="U33" s="23" t="n">
+      <c r="U33" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>U0187</t>
+          <t>U0166</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>HAYDEE RIMAC ALBERTO</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
+          <t>EUGENIO LEONCIO MOYA DURAND</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -3063,65 +3085,61 @@
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>Alberto Lop*</t>
+          <t>Llitech Moy*</t>
         </is>
       </c>
       <c r="G34" s="17" t="n"/>
       <c r="H34" s="18" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="I34" s="18" t="n"/>
       <c r="J34" s="19" t="inlineStr">
         <is>
-          <t>Haydee Rimac Alberto.    Mz J.    Lt. 7</t>
+          <t>Mz: i - Lt: 4</t>
         </is>
       </c>
       <c r="K34" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 16:33:15</t>
+          <t>06/06/2026 20:46:49</t>
         </is>
       </c>
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O34" s="21" t="n"/>
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="22" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R34" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S34" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T34" s="4" t="n"/>
-      <c r="U34" s="23" t="n">
+      <c r="U34" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>U0064</t>
-        </is>
-      </c>
+      <c r="A35" s="14" t="n"/>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>EBER AGÜERO TRUJILLO</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
+          <t>SAORY RAPRAY SILVA</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -3134,67 +3152,67 @@
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>Eber Agu*</t>
+          <t>Melissa Pil*</t>
         </is>
       </c>
       <c r="G35" s="17" t="n"/>
       <c r="H35" s="18" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="I35" s="18" t="n"/>
       <c r="J35" s="19" t="inlineStr">
         <is>
-          <t>MZ. C LTE. 34 Faena exonerado</t>
+          <t>Melissa MZB Lt 15</t>
         </is>
       </c>
       <c r="K35" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 14:00:31</t>
+          <t>06/06/2026 19:19:54</t>
         </is>
       </c>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O35" s="21" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R35" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="S35" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S35" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T35" s="4" t="n"/>
-      <c r="U35" s="23" t="n">
+      <c r="U35" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>U0059</t>
+          <t>U0446</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>OSTIN AGÜERO TRUJILLO</t>
+          <t>AUBERTINA TRUJILLO TOLENTINO</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
@@ -3205,67 +3223,67 @@
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>Eber Agu*</t>
+          <t>PLIN - WILLIAM MANUEL CUADROS CERREPE</t>
         </is>
       </c>
       <c r="G36" s="17" t="n"/>
       <c r="H36" s="18" t="n">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="I36" s="18" t="n"/>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>MZ. C LTE. 28</t>
+          <t>Aubertina Trujillo T</t>
         </is>
       </c>
       <c r="K36" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 13:59:09</t>
+          <t>06/06/2026 18:48:11</t>
         </is>
       </c>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O36" s="21" t="n"/>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R36" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S36" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T36" s="4" t="n"/>
-      <c r="U36" s="23" t="n">
+      <c r="U36" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>U0038</t>
+          <t>U0393</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>VICTOR LOPEZ TRUJILLO</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>FELIPE JESUS ORTIZ APONTE</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D37" s="4" t="n"/>
@@ -3276,65 +3294,65 @@
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>Katherine Vil*</t>
+          <t>Felipe Ort*</t>
         </is>
       </c>
       <c r="G37" s="17" t="n"/>
       <c r="H37" s="18" t="n">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="I37" s="18" t="n"/>
       <c r="J37" s="19" t="inlineStr">
         <is>
-          <t>mz C lt 7</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K37" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 12:26:01</t>
+          <t>06/06/2026 17:49:18</t>
         </is>
       </c>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O37" s="21" t="n"/>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="22" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="R37" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="S37" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S37" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T37" s="4" t="n"/>
-      <c r="U37" s="23" t="n">
+      <c r="U37" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>U0067</t>
+          <t>U0097</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>RAQUEL SORIA BUSTAMANTE</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
+          <t>TEOFILA FERNANDEZ REYES</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -3347,67 +3365,67 @@
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>Mery Bus*</t>
+          <t>Grabiela Val*</t>
         </is>
       </c>
       <c r="G38" s="17" t="n"/>
       <c r="H38" s="18" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I38" s="18" t="n"/>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>MZC    LT 37 ..raquel Valery Soria Bustamante</t>
+          <t xml:space="preserve">TEOFILA FERNANDEZ REYES MZ E Lt12 la loza se va </t>
         </is>
       </c>
       <c r="K38" s="17" t="inlineStr">
         <is>
-          <t>06/06/2026 12:14:12</t>
+          <t>06/06/2026 17:23:01</t>
         </is>
       </c>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" s="21" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="22" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R38" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S38" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T38" s="4" t="n"/>
-      <c r="U38" s="23" t="n">
+      <c r="U38" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>U0208</t>
+          <t>U0372</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>MARCIAL SANCHEZ ARAOZ</t>
-        </is>
-      </c>
-      <c r="C39" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>RENATO ALBORNOS SIGUEÑAS</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D39" s="4" t="n"/>
@@ -3418,62 +3436,62 @@
       </c>
       <c r="F39" s="17" t="inlineStr">
         <is>
-          <t>PLIN - GIOVANNA VANESSA SANCHEZ MEZA</t>
+          <t>Marisol Rom*</t>
         </is>
       </c>
       <c r="G39" s="17" t="n"/>
       <c r="H39" s="18" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="I39" s="18" t="n"/>
       <c r="J39" s="19" t="inlineStr">
         <is>
-          <t>Marcial Sánchez Aráoz Mk lt 17</t>
+          <t>Mzn.W.Lt.5</t>
         </is>
       </c>
       <c r="K39" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 20:39:00</t>
+          <t>06/06/2026 16:53:38</t>
         </is>
       </c>
       <c r="L39" s="4" t="n"/>
       <c r="M39" s="20" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>W</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O39" s="21" t="n"/>
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="22" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R39" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S39" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T39" s="4" t="n"/>
-      <c r="U39" s="23" t="n">
+      <c r="U39" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>U0431</t>
+          <t>U0434</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>DIEGO LÓPEZ MUÑOZ</t>
+          <t>JOHAN ENSO RODRIGUEZ FLORES</t>
         </is>
       </c>
       <c r="C40" s="25" t="inlineStr">
@@ -3489,65 +3507,65 @@
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>AGORA - DIEGO FABRICIO LOPEZ MUNOZ</t>
+          <t>Johan Rod*</t>
         </is>
       </c>
       <c r="G40" s="17" t="n"/>
       <c r="H40" s="18" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="I40" s="18" t="n"/>
       <c r="J40" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MZ, B1.Lt..3=Johan Rodriguez Flores</t>
         </is>
       </c>
       <c r="K40" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 18:42:50</t>
+          <t>06/06/2026 16:35:56</t>
         </is>
       </c>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="20" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O40" s="21" t="n"/>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="22" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R40" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S40" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T40" s="4" t="n"/>
-      <c r="U40" s="23" t="n">
+      <c r="U40" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>U0225</t>
+          <t>U0187</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>MERCURIO LUNA FLORES</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
+          <t>HAYDEE RIMAC ALBERTO</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -3560,67 +3578,67 @@
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>Jose Gre*</t>
+          <t>Alberto Lop*</t>
         </is>
       </c>
       <c r="G41" s="17" t="n"/>
       <c r="H41" s="18" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I41" s="18" t="n"/>
       <c r="J41" s="19" t="inlineStr">
         <is>
-          <t>usuario : mercurio luna flores mz.m Lt3</t>
+          <t>Haydee Rimac Alberto.    Mz J.    Lt. 7</t>
         </is>
       </c>
       <c r="K41" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 18:11:18</t>
+          <t>06/06/2026 16:33:15</t>
         </is>
       </c>
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>J</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O41" s="21" t="n"/>
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="22" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R41" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S41" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T41" s="4" t="n"/>
-      <c r="U41" s="23" t="n">
+      <c r="U41" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>U0182</t>
+          <t>U0064</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>HECTOR AGÜERO TRUJILLO</t>
-        </is>
-      </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>EBER AGÜERO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D42" s="4" t="n"/>
@@ -3631,67 +3649,67 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>Hector Agu*</t>
+          <t>Eber Agu*</t>
         </is>
       </c>
       <c r="G42" s="17" t="n"/>
       <c r="H42" s="18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I42" s="18" t="n"/>
       <c r="J42" s="19" t="inlineStr">
         <is>
-          <t>mz..."J"    Lt..."2".</t>
+          <t>MZ. C LTE. 34 Faena exonerado</t>
         </is>
       </c>
       <c r="K42" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 17:35:56</t>
+          <t>06/06/2026 14:00:31</t>
         </is>
       </c>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="O42" s="21" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R42" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S42" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T42" s="4" t="n"/>
-      <c r="U42" s="23" t="n">
+      <c r="U42" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>U0065</t>
+          <t>U0059</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>ANALY QUINECHE MORANTE</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>OSTIN AGÜERO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D43" s="4" t="n"/>
@@ -3702,22 +3720,22 @@
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>PLIN - ANALI QUINECHE</t>
+          <t>Eber Agu*</t>
         </is>
       </c>
       <c r="G43" s="17" t="n"/>
       <c r="H43" s="18" t="n">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="I43" s="18" t="n"/>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MZ. C LTE. 28</t>
         </is>
       </c>
       <c r="K43" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 17:34:08</t>
+          <t>06/06/2026 13:59:09</t>
         </is>
       </c>
       <c r="L43" s="4" t="n"/>
@@ -3728,41 +3746,41 @@
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O43" s="21" t="n"/>
       <c r="P43" s="4" t="n"/>
       <c r="Q43" s="22" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="R43" s="22" t="n">
-        <v>-375</v>
-      </c>
-      <c r="S43" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S43" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T43" s="4" t="n"/>
-      <c r="U43" s="23" t="n">
+      <c r="U43" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>U0008</t>
+          <t>U0038</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>VICTOR MELGAREJO CORCINO</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>VICTOR LOPEZ TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D44" s="4" t="n"/>
@@ -3773,67 +3791,67 @@
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>Jesus Mel*</t>
+          <t>Katherine Vil*</t>
         </is>
       </c>
       <c r="G44" s="17" t="n"/>
       <c r="H44" s="18" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I44" s="18" t="n"/>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mz C lt 7</t>
         </is>
       </c>
       <c r="K44" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 12:34:58</t>
+          <t>06/06/2026 12:26:01</t>
         </is>
       </c>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O44" s="21" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="22" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R44" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S44" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T44" s="4" t="n"/>
-      <c r="U44" s="23" t="n">
+      <c r="U44" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>U0183</t>
+          <t>U0067</t>
         </is>
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>VILMA CELESTINO VILLAFANA</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>RAQUEL SORIA BUSTAMANTE</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D45" s="4" t="n"/>
@@ -3844,67 +3862,67 @@
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>PLIN - Vilma Norma Celestino Villafana</t>
+          <t>Mery Bus*</t>
         </is>
       </c>
       <c r="G45" s="17" t="n"/>
       <c r="H45" s="18" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I45" s="18" t="n"/>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MZC    LT 37 ..raquel Valery Soria Bustamante</t>
         </is>
       </c>
       <c r="K45" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 11:58:03</t>
+          <t>06/06/2026 12:14:12</t>
         </is>
       </c>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="20" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O45" s="21" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="22" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R45" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S45" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T45" s="4" t="n"/>
-      <c r="U45" s="23" t="n">
+      <c r="U45" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>U0017</t>
+          <t>U0208</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>POMPEYO CELESTINO LLIUYA</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>MARCIAL SANCHEZ ARAOZ</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D46" s="4" t="n"/>
@@ -3915,67 +3933,67 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>PLIN - Vilma Norma Celestino Villafana</t>
+          <t>PLIN - GIOVANNA VANESSA SANCHEZ MEZA</t>
         </is>
       </c>
       <c r="G46" s="17" t="n"/>
       <c r="H46" s="18" t="n">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="I46" s="18" t="n"/>
       <c r="J46" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marcial Sánchez Aráoz Mk lt 17</t>
         </is>
       </c>
       <c r="K46" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 11:54:46</t>
+          <t>05/06/2026 20:39:00</t>
         </is>
       </c>
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>K</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O46" s="21" t="n"/>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="22" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="R46" s="22" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S46" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S46" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T46" s="4" t="n"/>
-      <c r="U46" s="23" t="n">
+      <c r="U46" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>U0012</t>
+          <t>U0431</t>
         </is>
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>FELIX POZO CASTRO</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>DIEGO LÓPEZ MUÑOZ</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D47" s="4" t="n"/>
@@ -3986,67 +4004,67 @@
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>Felix Poz*</t>
+          <t>AGORA - DIEGO FABRICIO LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="G47" s="17" t="n"/>
       <c r="H47" s="18" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I47" s="18" t="n"/>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t>MZ ALT 11 felix pozo   revisar corte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K47" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 11:12:37</t>
+          <t>05/06/2026 18:42:50</t>
         </is>
       </c>
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O47" s="21" t="n"/>
       <c r="P47" s="4" t="n"/>
       <c r="Q47" s="22" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R47" s="22" t="n">
-        <v>-40</v>
-      </c>
-      <c r="S47" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S47" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T47" s="4" t="n"/>
-      <c r="U47" s="23" t="n">
+      <c r="U47" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>U0041</t>
+          <t>U0225</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>JUAN UCULMANA SANCHEZ</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>MERCURIO LUNA FLORES</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D48" s="4" t="n"/>
@@ -4057,62 +4075,62 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>BCP - UCULMANA GOMEZ OLGA ESTHER</t>
+          <t>Jose Gre*</t>
         </is>
       </c>
       <c r="G48" s="17" t="n"/>
       <c r="H48" s="18" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="I48" s="18" t="n"/>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>Pagos de gastos de agua y multas casa tupac</t>
+          <t>usuario : mercurio luna flores mz.m Lt3</t>
         </is>
       </c>
       <c r="K48" s="17" t="inlineStr">
         <is>
-          <t>05/06/2026 03:13:22</t>
+          <t>05/06/2026 18:11:18</t>
         </is>
       </c>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O48" s="21" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="22" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R48" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S48" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T48" s="4" t="n"/>
-      <c r="U48" s="23" t="n">
+      <c r="U48" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>U0053</t>
+          <t>U0182</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>ABRAHAM BARRERA VEGA</t>
+          <t>HECTOR AGÜERO TRUJILLO</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
@@ -4128,67 +4146,67 @@
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>Francisco Acu*</t>
+          <t>Hector Agu*</t>
         </is>
       </c>
       <c r="G49" s="17" t="n"/>
       <c r="H49" s="18" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I49" s="18" t="n"/>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mz..."J"    Lt..."2".</t>
         </is>
       </c>
       <c r="K49" s="17" t="inlineStr">
         <is>
-          <t>04/06/2026 15:37:58</t>
+          <t>05/06/2026 17:35:56</t>
         </is>
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O49" s="21" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R49" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S49" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T49" s="4" t="n"/>
-      <c r="U49" s="23" t="n">
+      <c r="U49" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>U0173</t>
+          <t>U0065</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>DOMINGA CHACARA LOPEZ</t>
+          <t>ANALY QUINECHE MORANTE</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D50" s="4" t="n"/>
@@ -4199,67 +4217,67 @@
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>Juan Rio*</t>
+          <t>PLIN - ANALI QUINECHE</t>
         </is>
       </c>
       <c r="G50" s="17" t="n"/>
       <c r="H50" s="18" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="I50" s="18" t="n"/>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>Dominga chaccara López mz i lote 11</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
-          <t>03/06/2026 20:52:08</t>
+          <t>05/06/2026 17:34:08</t>
         </is>
       </c>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O50" s="21" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="22" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R50" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S50" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T50" s="4" t="n"/>
-      <c r="U50" s="23" t="n">
+      <c r="U50" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>U0405</t>
+          <t>U0008</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>FELIX LUNA LOPEZ</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>VICTOR MELGAREJO CORCINO</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D51" s="4" t="n"/>
@@ -4270,12 +4288,12 @@
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>Maria Alv*</t>
+          <t>Jesus Mel*</t>
         </is>
       </c>
       <c r="G51" s="17" t="n"/>
       <c r="H51" s="18" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I51" s="18" t="n"/>
       <c r="J51" s="19" t="inlineStr">
@@ -4285,52 +4303,52 @@
       </c>
       <c r="K51" s="17" t="inlineStr">
         <is>
-          <t>03/06/2026 19:50:28</t>
+          <t>05/06/2026 12:34:58</t>
         </is>
       </c>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="20" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O51" s="21" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R51" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S51" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T51" s="4" t="n"/>
-      <c r="U51" s="23" t="n">
+      <c r="U51" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>U0066</t>
+          <t>U0183</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>MARIA NORABUENA ESPADA</t>
+          <t>VILMA CELESTINO VILLAFANA</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D52" s="4" t="n"/>
@@ -4341,67 +4359,67 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>BCP - JACOME NORABUENA JESUS ELVIRO</t>
+          <t>PLIN - Vilma Norma Celestino Villafana</t>
         </is>
       </c>
       <c r="G52" s="17" t="n"/>
       <c r="H52" s="18" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="I52" s="18" t="n"/>
       <c r="J52" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA NORABUENA ESPADA   Mz C Lt 36    N. recibo 16992      </t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K52" s="17" t="inlineStr">
         <is>
-          <t>03/06/2026 18:24:18</t>
+          <t>05/06/2026 11:58:03</t>
         </is>
       </c>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O52" s="21" t="n"/>
       <c r="P52" s="4" t="n"/>
       <c r="Q52" s="22" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R52" s="22" t="n">
-        <v>-125</v>
-      </c>
-      <c r="S52" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S52" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T52" s="4" t="n"/>
-      <c r="U52" s="23" t="n">
+      <c r="U52" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>U0499</t>
+          <t>U0017</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>TITO COSME CASTILLEJO</t>
+          <t>POMPEYO CELESTINO LLIUYA</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D53" s="4" t="n"/>
@@ -4412,65 +4430,65 @@
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>Nancy Mon*</t>
+          <t>PLIN - Vilma Norma Celestino Villafana</t>
         </is>
       </c>
       <c r="G53" s="17" t="n"/>
       <c r="H53" s="18" t="n">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="I53" s="18" t="n"/>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t>Tito cosme castillejo Mz.H1.Lt.36</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K53" s="17" t="inlineStr">
         <is>
-          <t>03/06/2026 16:20:52</t>
+          <t>05/06/2026 11:54:46</t>
         </is>
       </c>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="20" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O53" s="21" t="n"/>
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="22" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R53" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S53" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T53" s="4" t="n"/>
-      <c r="U53" s="23" t="n">
+      <c r="U53" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>U0222</t>
+          <t>U0012</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>AGUSTINA CALDAS CORZO</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
+          <t>FELIX POZO CASTRO</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -4483,67 +4501,67 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>Hellen Val*</t>
+          <t>Felix Poz*</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>
       <c r="H54" s="18" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="I54" s="18" t="n"/>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>AGUSTINA CALDAS CORZO  MZ "L" LT "15"</t>
+          <t>MZ ALT 11 felix pozo   revisar corte</t>
         </is>
       </c>
       <c r="K54" s="17" t="inlineStr">
         <is>
-          <t>03/06/2026 15:27:57</t>
+          <t>05/06/2026 11:12:37</t>
         </is>
       </c>
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="20" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O54" s="21" t="n"/>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R54" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S54" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T54" s="4" t="n"/>
-      <c r="U54" s="23" t="n">
+      <c r="U54" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>U0337</t>
+          <t>U0041</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>RIVET VILLANUEVA ALEGRIA</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>JUAN UCULMANA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
@@ -4554,67 +4572,67 @@
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>Rivet Vil*</t>
+          <t>BCP - UCULMANA GOMEZ OLGA ESTHER</t>
         </is>
       </c>
       <c r="G55" s="17" t="n"/>
       <c r="H55" s="18" t="n">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="I55" s="18" t="n"/>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t>mz T Lt 11</t>
+          <t>Pagos de gastos de agua y multas casa tupac</t>
         </is>
       </c>
       <c r="K55" s="17" t="inlineStr">
         <is>
-          <t>03/06/2026 11:05:43</t>
+          <t>05/06/2026 03:13:22</t>
         </is>
       </c>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="20" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O55" s="21" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R55" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="16" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S55" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T55" s="4" t="n"/>
-      <c r="U55" s="23" t="n">
+      <c r="U55" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>U0178</t>
+          <t>U0053</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>ADOLFO ROSARIO ROJAS</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>ABRAHAM BARRERA VEGA</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D56" s="4" t="n"/>
@@ -4625,12 +4643,12 @@
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>Adolfo Ros*</t>
+          <t>Francisco Acu*</t>
         </is>
       </c>
       <c r="G56" s="17" t="n"/>
       <c r="H56" s="18" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I56" s="18" t="n"/>
       <c r="J56" s="19" t="inlineStr">
@@ -4640,48 +4658,52 @@
       </c>
       <c r="K56" s="17" t="inlineStr">
         <is>
-          <t>02/06/2026 07:44:53</t>
+          <t>04/06/2026 15:37:58</t>
         </is>
       </c>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O56" s="21" t="n"/>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="22" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="R56" s="22" t="n">
-        <v>-118</v>
-      </c>
-      <c r="S56" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S56" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T56" s="4" t="n"/>
-      <c r="U56" s="23" t="n">
+      <c r="U56" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="14" t="n"/>
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>U0173</t>
+        </is>
+      </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>IGLESIA EVANGELICA BAUTISTA</t>
-        </is>
-      </c>
-      <c r="C57" s="23" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>DOMINGA CHACARA LOPEZ</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D57" s="4" t="n"/>
@@ -4692,33 +4714,33 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Ramon Req*</t>
+          <t>Juan Rio*</t>
         </is>
       </c>
       <c r="G57" s="17" t="n"/>
       <c r="H57" s="18" t="n">
-        <v>266</v>
+        <v>88</v>
       </c>
       <c r="I57" s="18" t="n"/>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t>del 2019 hasta octubre 2025</t>
+          <t>Dominga chaccara López mz i lote 11</t>
         </is>
       </c>
       <c r="K57" s="17" t="inlineStr">
         <is>
-          <t>01/06/2026 18:34:12</t>
+          <t>03/06/2026 20:52:08</t>
         </is>
       </c>
       <c r="L57" s="4" t="n"/>
       <c r="M57" s="20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>I</t>
         </is>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O57" s="21" t="n"/>
@@ -4729,30 +4751,30 @@
       <c r="R57" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="28" t="inlineStr">
+      <c r="S57" s="23" t="inlineStr">
         <is>
           <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T57" s="4" t="n"/>
-      <c r="U57" s="23" t="n">
+      <c r="U57" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>U0020</t>
+          <t>U0405</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>ROSALINA OLIMPIA CIRIACO SOTELO</t>
+          <t>FELIX LUNA LOPEZ</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D58" s="4" t="n"/>
@@ -4763,65 +4785,65 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>Rosalina Cir*</t>
+          <t>Maria Alv*</t>
         </is>
       </c>
       <c r="G58" s="17" t="n"/>
       <c r="H58" s="18" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I58" s="18" t="n"/>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>Mz.b Lt8 ROSALINA CIRIACO SOTELO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K58" s="17" t="inlineStr">
         <is>
-          <t>30/05/2026 11:41:28</t>
+          <t>03/06/2026 19:50:28</t>
         </is>
       </c>
       <c r="L58" s="4" t="n"/>
       <c r="M58" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O58" s="21" t="n"/>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="22" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R58" s="22" t="n">
-        <v>-98</v>
-      </c>
-      <c r="S58" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S58" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T58" s="4" t="n"/>
-      <c r="U58" s="23" t="n">
+      <c r="U58" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>U0455</t>
+          <t>U0066</t>
         </is>
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>EVER CERVANTES CHAVES</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
+          <t>MARIA NORABUENA ESPADA</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -4834,65 +4856,65 @@
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>Ever Cer*</t>
+          <t>BCP - JACOME NORABUENA JESUS ELVIRO</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
       <c r="H59" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I59" s="18" t="n"/>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t>MZ C1 LT 15</t>
+          <t xml:space="preserve">MARIA NORABUENA ESPADA   Mz C Lt 36    N. recibo 16992      </t>
         </is>
       </c>
       <c r="K59" s="17" t="inlineStr">
         <is>
-          <t>27/05/2026 07:00:40</t>
+          <t>03/06/2026 18:24:18</t>
         </is>
       </c>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="20" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O59" s="21" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="22" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R59" s="22" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S59" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S59" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T59" s="4" t="n"/>
-      <c r="U59" s="23" t="n">
+      <c r="U59" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>U0417</t>
+          <t>U0499</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>ROSA DURAND SALES</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
+          <t>TITO COSME CASTILLEJO</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -4905,65 +4927,65 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>Carolyn Mar*</t>
+          <t>Nancy Mon*</t>
         </is>
       </c>
       <c r="G60" s="17" t="n"/>
       <c r="H60" s="18" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="I60" s="18" t="n"/>
       <c r="J60" s="19" t="inlineStr">
         <is>
-          <t>Mz Z Lt.14</t>
+          <t>Tito cosme castillejo Mz.H1.Lt.36</t>
         </is>
       </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
-          <t>22/05/2026 18:17:44</t>
+          <t>03/06/2026 16:20:52</t>
         </is>
       </c>
       <c r="L60" s="4" t="n"/>
       <c r="M60" s="20" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O60" s="21" t="n"/>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="22" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R60" s="22" t="n">
-        <v>-82</v>
-      </c>
-      <c r="S60" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S60" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T60" s="4" t="n"/>
-      <c r="U60" s="23" t="n">
+      <c r="U60" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>U0229</t>
+          <t>U0222</t>
         </is>
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>VICTORIA COCHACHIN CASIO</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
+          <t>AGUSTINA CALDAS CORZO</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
         <is>
           <t>mensaje</t>
         </is>
@@ -4976,50 +4998,543 @@
       </c>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>Brilly Pan*</t>
+          <t>Hellen Val*</t>
         </is>
       </c>
       <c r="G61" s="17" t="n"/>
       <c r="H61" s="18" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I61" s="18" t="n"/>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t>victoria cochachin   mz:M  lt:7</t>
+          <t>AGUSTINA CALDAS CORZO  MZ "L" LT "15"</t>
         </is>
       </c>
       <c r="K61" s="17" t="inlineStr">
         <is>
-          <t>19/05/2026 19:14:27</t>
+          <t>03/06/2026 15:27:57</t>
         </is>
       </c>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O61" s="21" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R61" s="22" t="n">
-        <v>-24</v>
-      </c>
-      <c r="S61" s="27" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S61" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T61" s="4" t="n"/>
-      <c r="U61" s="23" t="n">
+      <c r="U61" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>U0337</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>RIVET VILLANUEVA ALEGRIA</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>Rivet Vil*</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="n"/>
+      <c r="H62" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="I62" s="18" t="n"/>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>mz T Lt 11</t>
+        </is>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
+        <is>
+          <t>03/06/2026 11:05:43</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O62" s="21" t="n"/>
+      <c r="P62" s="4" t="n"/>
+      <c r="Q62" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>U0178</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>ADOLFO ROSARIO ROJAS</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>correccion</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>Adolfo Ros*</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="n"/>
+      <c r="H63" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K63" s="17" t="inlineStr">
+        <is>
+          <t>02/06/2026 07:44:53</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O63" s="21" t="n"/>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T63" s="4" t="n"/>
+      <c r="U63" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="14" t="n"/>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>IGLESIA EVANGELICA BAUTISTA</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>correccion</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>Ramon Req*</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="n"/>
+      <c r="H64" s="18" t="n">
+        <v>266</v>
+      </c>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>del 2019 hasta octubre 2025</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
+        <is>
+          <t>01/06/2026 18:34:12</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n"/>
+      <c r="P64" s="4" t="n"/>
+      <c r="Q64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>U0020</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>ROSALINA OLIMPIA CIRIACO SOTELO</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>Rosalina Cir*</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="n"/>
+      <c r="H65" s="18" t="n">
+        <v>46</v>
+      </c>
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>Mz.b Lt8 ROSALINA CIRIACO SOTELO</t>
+        </is>
+      </c>
+      <c r="K65" s="17" t="inlineStr">
+        <is>
+          <t>30/05/2026 11:41:28</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O65" s="21" t="n"/>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T65" s="4" t="n"/>
+      <c r="U65" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>U0455</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>EVER CERVANTES CHAVES</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>Ever Cer*</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>MZ C1 LT 15</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>27/05/2026 07:00:40</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="20" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="n"/>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>U0417</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>ROSA DURAND SALES</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>Carolyn Mar*</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="n"/>
+      <c r="H67" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>Mz Z Lt.14</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
+        <is>
+          <t>22/05/2026 18:17:44</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="20" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="N67" s="20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O67" s="21" t="n"/>
+      <c r="P67" s="4" t="n"/>
+      <c r="Q67" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T67" s="4" t="n"/>
+      <c r="U67" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>U0229</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>VICTORIA COCHACHIN CASIO</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>mensaje</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>Brilly Pan*</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="n"/>
+      <c r="H68" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>victoria cochachin   mz:M  lt:7</t>
+        </is>
+      </c>
+      <c r="K68" s="17" t="inlineStr">
+        <is>
+          <t>19/05/2026 19:14:27</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N68" s="20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O68" s="21" t="n"/>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="23" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5040,7 +5555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5191,7 +5706,7 @@
       </c>
       <c r="L3" s="29" t="n"/>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="23" t="n">
+      <c r="N3" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5235,7 +5750,7 @@
       </c>
       <c r="L4" s="29" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="23" t="n">
+      <c r="N4" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5279,7 +5794,7 @@
       </c>
       <c r="L5" s="29" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="23" t="n">
+      <c r="N5" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5323,7 +5838,7 @@
       </c>
       <c r="L6" s="29" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="23" t="n">
+      <c r="N6" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5367,7 +5882,7 @@
       </c>
       <c r="L7" s="29" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="23" t="n">
+      <c r="N7" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5411,7 +5926,7 @@
       </c>
       <c r="L8" s="29" t="n"/>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="23" t="n">
+      <c r="N8" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5455,7 +5970,7 @@
       </c>
       <c r="L9" s="29" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="23" t="n">
+      <c r="N9" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5503,7 +6018,7 @@
       <c r="K10" s="29" t="n"/>
       <c r="L10" s="29" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="23" t="n">
+      <c r="N10" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5547,7 +6062,7 @@
       </c>
       <c r="L11" s="29" t="n"/>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="23" t="n">
+      <c r="N11" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5591,7 +6106,7 @@
       </c>
       <c r="L12" s="29" t="n"/>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="23" t="n">
+      <c r="N12" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5635,7 +6150,7 @@
       </c>
       <c r="L13" s="29" t="n"/>
       <c r="M13" s="4" t="n"/>
-      <c r="N13" s="23" t="n">
+      <c r="N13" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5679,7 +6194,7 @@
       </c>
       <c r="L14" s="29" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="23" t="n">
+      <c r="N14" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5723,7 +6238,139 @@
       </c>
       <c r="L15" s="29" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="23" t="n">
+      <c r="N15" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>PAGASTE</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Janet Vil*</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Raul Bla*</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>ferretería raul</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>19/06/2026 20:27:41</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="29" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="L16" s="29" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>PAGASTE</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Janet Vil*</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Raul Bla*</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>ferretería raul</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>19/06/2026 20:26:42</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="29" t="inlineStr">
+        <is>
+          <t>mantenimiento</t>
+        </is>
+      </c>
+      <c r="L17" s="29" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>PAGASTE</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Janet Vil*</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Dedicacion Gar*</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>bebidas para faena</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:11:59</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="29" t="inlineStr">
+        <is>
+          <t>viatico faena</t>
+        </is>
+      </c>
+      <c r="L18" s="29" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="16" t="n">
         <v>2</v>
       </c>
     </row>
